--- a/docs/Files/ODYM_Tutorial6_SectorSplitLL_V1.0.xlsx
+++ b/docs/Files/ODYM_Tutorial6_SectorSplitLL_V1.0.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A605B08C-FD6E-4179-A3BF-7DACBF530B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70DD2510-8798-4357-9675-52225BC7710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="107">
   <si>
     <t>Format_Version</t>
   </si>
@@ -201,36 +201,15 @@
     <t>none</t>
   </si>
   <si>
-    <t>Automotive steel</t>
-  </si>
-  <si>
     <t>Waste mgt. Industries</t>
   </si>
   <si>
     <t>BAU</t>
   </si>
   <si>
-    <t>Efficient</t>
-  </si>
-  <si>
     <t>Scenario</t>
   </si>
   <si>
-    <t>vehicles</t>
-  </si>
-  <si>
-    <t>machinery</t>
-  </si>
-  <si>
-    <t>construction</t>
-  </si>
-  <si>
-    <t>products and other</t>
-  </si>
-  <si>
-    <t>Construction grade steel</t>
-  </si>
-  <si>
     <t>value in 1 (%)</t>
   </si>
   <si>
@@ -358,12 +337,6 @@
   </si>
   <si>
     <t>From dataset 4_PY_FabricationYield_Cullen2012, value for "Industrial equipment", assuming that construction steel only goes to constrution and machinery</t>
-  </si>
-  <si>
-    <t>From dataset 4_PY_FabricationYield_Cullen2012, average value for "Construction", assuming that construction steel only goes to constrution and machinery</t>
-  </si>
-  <si>
-    <t>assuming that automotive steel only goes to vehicles</t>
   </si>
   <si>
     <t>ODYM_Classifications_LL</t>
@@ -467,7 +440,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -488,8 +461,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -836,7 +808,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>16</v>
@@ -850,7 +822,7 @@
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
@@ -906,7 +878,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>16</v>
@@ -920,7 +892,7 @@
         <v>24</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>16</v>
@@ -934,7 +906,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>16</v>
@@ -1004,7 +976,7 @@
         <v>36</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>16</v>
@@ -1082,16 +1054,16 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>16</v>
@@ -1102,16 +1074,16 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D24" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>16</v>
@@ -1122,16 +1094,16 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>16</v>
@@ -1177,7 +1149,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
@@ -1194,13 +1166,13 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>11</v>
@@ -1219,14 +1191,14 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>114</v>
+      <c r="A2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="D2">
         <v>0.9</v>
@@ -1241,18 +1213,18 @@
         <v>55</v>
       </c>
       <c r="H2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>115</v>
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>106</v>
       </c>
       <c r="D3">
         <v>0.1</v>
@@ -1267,18 +1239,18 @@
         <v>55</v>
       </c>
       <c r="H3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>114</v>
+      <c r="A4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="D4">
         <v>0.2</v>
@@ -1293,18 +1265,18 @@
         <v>55</v>
       </c>
       <c r="H4" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>115</v>
+      <c r="A5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>106</v>
       </c>
       <c r="D5">
         <v>0.8</v>
@@ -1319,219 +1291,11 @@
         <v>55</v>
       </c>
       <c r="H5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>55</v>
-      </c>
-      <c r="H6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>55</v>
-      </c>
-      <c r="H7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9" t="s">
-        <v>55</v>
-      </c>
-      <c r="H9" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>55</v>
-      </c>
-      <c r="H10" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>55</v>
-      </c>
-      <c r="H11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
-        <v>55</v>
-      </c>
-      <c r="H12" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" t="s">
-        <v>64</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13" t="s">
-        <v>55</v>
-      </c>
-      <c r="H13" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="31" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E31" s="1"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E23" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1545,40 +1309,40 @@
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.35">
@@ -1590,13 +1354,13 @@
       </c>
       <c r="E3" s="15"/>
       <c r="F3" s="12" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="G3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1611,58 +1375,58 @@
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="N2" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
